--- a/data-hotel.xlsx
+++ b/data-hotel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Donnée 2025\yeiayel consulting\Excel\LAHIMENA TOURS\Excel\Lahimena\ApiOK\Lahimena\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1911C06D-AD0F-4B91-AFE7-63DFA17707CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35FEF6F9-0691-4310-AFD3-53CFDF86C735}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BDD_HOTEL" sheetId="1" r:id="rId1"/>
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="661" uniqueCount="241">
   <si>
     <t>Hotel</t>
   </si>
@@ -698,12 +698,6 @@
     <t>MONTANT</t>
   </si>
   <si>
-    <t>QUANTITE</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
     <t>TRAJET</t>
   </si>
   <si>
@@ -795,6 +789,24 @@
   </si>
   <si>
     <t>Tarif Bébé</t>
+  </si>
+  <si>
+    <t>Forfait 1</t>
+  </si>
+  <si>
+    <t>Travels guide Mada</t>
+  </si>
+  <si>
+    <t>Guide full options</t>
+  </si>
+  <si>
+    <t>Forfait 2</t>
+  </si>
+  <si>
+    <t>Travels d'Anosy</t>
+  </si>
+  <si>
+    <t>Guide full fort dauphin</t>
   </si>
 </sst>
 </file>
@@ -1029,7 +1041,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="61">
+  <borders count="60">
     <border>
       <left/>
       <right/>
@@ -1580,19 +1592,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </right>
-      <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </top>
-      <bottom style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -2063,137 +2062,137 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="47" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="47" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="20" borderId="47" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="47" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="20" borderId="47" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="47" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="57" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="10" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="10" fillId="0" borderId="58" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="10" fillId="0" borderId="59" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="10" fillId="20" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="10" fillId="20" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="11" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="12" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="13" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="20" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="48" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="20" borderId="48" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="10" fillId="0" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="10" fillId="0" borderId="59" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="10" fillId="0" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="10" fillId="20" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="10" fillId="20" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Milliers" xfId="1" builtinId="3"/>
@@ -2505,24 +2504,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:49" ht="15" customHeight="1">
-      <c r="A1" s="170" t="s">
+      <c r="A1" s="211" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="171"/>
+      <c r="B1" s="212"/>
       <c r="C1" s="1"/>
-      <c r="D1" s="172"/>
-      <c r="E1" s="173"/>
+      <c r="D1" s="213"/>
+      <c r="E1" s="209"/>
       <c r="F1" s="2"/>
-      <c r="G1" s="174" t="s">
+      <c r="G1" s="214" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="175"/>
-      <c r="I1" s="175"/>
-      <c r="J1" s="175"/>
-      <c r="K1" s="175"/>
-      <c r="L1" s="175"/>
-      <c r="M1" s="175"/>
-      <c r="N1" s="175"/>
+      <c r="H1" s="206"/>
+      <c r="I1" s="206"/>
+      <c r="J1" s="206"/>
+      <c r="K1" s="206"/>
+      <c r="L1" s="206"/>
+      <c r="M1" s="206"/>
+      <c r="N1" s="206"/>
       <c r="O1" s="3"/>
       <c r="P1" s="3"/>
       <c r="Q1" s="3"/>
@@ -2532,43 +2531,43 @@
       <c r="S1" s="3"/>
       <c r="T1" s="3"/>
       <c r="U1" s="3"/>
-      <c r="V1" s="176" t="s">
+      <c r="V1" s="215" t="s">
         <v>3</v>
       </c>
-      <c r="W1" s="175"/>
-      <c r="X1" s="175"/>
-      <c r="Y1" s="175"/>
-      <c r="Z1" s="175"/>
-      <c r="AA1" s="173"/>
-      <c r="AB1" s="177" t="s">
+      <c r="W1" s="206"/>
+      <c r="X1" s="206"/>
+      <c r="Y1" s="206"/>
+      <c r="Z1" s="206"/>
+      <c r="AA1" s="209"/>
+      <c r="AB1" s="216" t="s">
         <v>4</v>
       </c>
-      <c r="AC1" s="175"/>
-      <c r="AD1" s="175"/>
-      <c r="AE1" s="175"/>
-      <c r="AF1" s="175"/>
-      <c r="AG1" s="175"/>
-      <c r="AH1" s="175"/>
-      <c r="AI1" s="173"/>
-      <c r="AJ1" s="178" t="s">
+      <c r="AC1" s="206"/>
+      <c r="AD1" s="206"/>
+      <c r="AE1" s="206"/>
+      <c r="AF1" s="206"/>
+      <c r="AG1" s="206"/>
+      <c r="AH1" s="206"/>
+      <c r="AI1" s="209"/>
+      <c r="AJ1" s="205" t="s">
         <v>5</v>
       </c>
-      <c r="AK1" s="175"/>
-      <c r="AL1" s="175"/>
-      <c r="AM1" s="175"/>
-      <c r="AN1" s="175"/>
-      <c r="AO1" s="175"/>
-      <c r="AP1" s="179"/>
+      <c r="AK1" s="206"/>
+      <c r="AL1" s="206"/>
+      <c r="AM1" s="206"/>
+      <c r="AN1" s="206"/>
+      <c r="AO1" s="206"/>
+      <c r="AP1" s="207"/>
       <c r="AQ1" s="5"/>
-      <c r="AR1" s="180" t="s">
+      <c r="AR1" s="208" t="s">
         <v>6</v>
       </c>
-      <c r="AS1" s="173"/>
-      <c r="AT1" s="181" t="s">
+      <c r="AS1" s="209"/>
+      <c r="AT1" s="210" t="s">
         <v>7</v>
       </c>
-      <c r="AU1" s="175"/>
-      <c r="AV1" s="173"/>
+      <c r="AU1" s="206"/>
+      <c r="AV1" s="209"/>
       <c r="AW1" s="6" t="s">
         <v>8</v>
       </c>
@@ -55301,35 +55300,65 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD13627D-438B-41F0-96BA-63674847DC7B}">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24.140625" customWidth="1"/>
     <col min="2" max="2" width="45.42578125" customWidth="1"/>
     <col min="3" max="3" width="20.7109375" customWidth="1"/>
     <col min="4" max="4" width="22" customWidth="1"/>
-    <col min="5" max="5" width="16.42578125" customWidth="1"/>
-    <col min="6" max="6" width="17.140625" customWidth="1"/>
+    <col min="5" max="5" width="17.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="182" t="s">
+    <row r="1" spans="1:5">
+      <c r="A1" s="170" t="s">
         <v>200</v>
       </c>
-      <c r="B1" s="183" t="s">
+      <c r="B1" s="171" t="s">
         <v>201</v>
       </c>
-      <c r="C1" s="183" t="s">
+      <c r="C1" s="171" t="s">
         <v>202</v>
       </c>
-      <c r="D1" s="183" t="s">
+      <c r="D1" s="171" t="s">
         <v>203</v>
       </c>
-      <c r="E1" s="183" t="s">
-        <v>204</v>
-      </c>
-      <c r="F1" s="184" t="s">
-        <v>205</v>
+      <c r="E1" s="228" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>235</v>
+      </c>
+      <c r="B2" t="s">
+        <v>236</v>
+      </c>
+      <c r="C2" t="s">
+        <v>237</v>
+      </c>
+      <c r="D2">
+        <v>300000</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>238</v>
+      </c>
+      <c r="B3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C3" t="s">
+        <v>240</v>
+      </c>
+      <c r="D3">
+        <v>200000</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -55358,131 +55387,131 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="185"/>
-      <c r="B1" s="185"/>
-      <c r="C1" s="186" t="s">
+      <c r="A1" s="172"/>
+      <c r="B1" s="172"/>
+      <c r="C1" s="217" t="s">
+        <v>204</v>
+      </c>
+      <c r="D1" s="217"/>
+      <c r="E1" s="218" t="s">
+        <v>205</v>
+      </c>
+      <c r="F1" s="218"/>
+      <c r="G1" s="218"/>
+      <c r="H1" s="219"/>
+      <c r="I1" s="222" t="s">
         <v>206</v>
       </c>
-      <c r="D1" s="186"/>
-      <c r="E1" s="187" t="s">
+      <c r="J1" s="222"/>
+      <c r="K1" s="224" t="s">
         <v>207</v>
       </c>
-      <c r="F1" s="187"/>
-      <c r="G1" s="187"/>
-      <c r="H1" s="188"/>
-      <c r="I1" s="189" t="s">
+      <c r="L1" s="225"/>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="172"/>
+      <c r="B2" s="172"/>
+      <c r="C2" s="217"/>
+      <c r="D2" s="217"/>
+      <c r="E2" s="220"/>
+      <c r="F2" s="220"/>
+      <c r="G2" s="220"/>
+      <c r="H2" s="221"/>
+      <c r="I2" s="223"/>
+      <c r="J2" s="223"/>
+      <c r="K2" s="226"/>
+      <c r="L2" s="227"/>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="173" t="s">
         <v>208</v>
       </c>
-      <c r="J1" s="189"/>
-      <c r="K1" s="190" t="s">
+      <c r="B3" s="174" t="s">
         <v>209</v>
       </c>
-      <c r="L1" s="191"/>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2" s="185"/>
-      <c r="B2" s="185"/>
-      <c r="C2" s="186"/>
-      <c r="D2" s="186"/>
-      <c r="E2" s="192"/>
-      <c r="F2" s="192"/>
-      <c r="G2" s="192"/>
-      <c r="H2" s="193"/>
-      <c r="I2" s="194"/>
-      <c r="J2" s="194"/>
-      <c r="K2" s="195"/>
-      <c r="L2" s="196"/>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="197" t="s">
+      <c r="C3" s="175" t="s">
         <v>210</v>
       </c>
-      <c r="B3" s="198" t="s">
+      <c r="D3" s="175" t="s">
         <v>211</v>
       </c>
-      <c r="C3" s="199" t="s">
+      <c r="E3" s="176" t="s">
         <v>212</v>
       </c>
-      <c r="D3" s="199" t="s">
+      <c r="F3" s="176" t="s">
+        <v>171</v>
+      </c>
+      <c r="G3" s="176" t="s">
         <v>213</v>
       </c>
-      <c r="E3" s="200" t="s">
+      <c r="H3" s="177" t="s">
         <v>214</v>
       </c>
-      <c r="F3" s="200" t="s">
-        <v>171</v>
-      </c>
-      <c r="G3" s="200" t="s">
+      <c r="I3" s="178" t="s">
         <v>215</v>
       </c>
-      <c r="H3" s="201" t="s">
+      <c r="J3" s="178" t="s">
         <v>216</v>
       </c>
-      <c r="I3" s="202" t="s">
+      <c r="K3" s="179" t="s">
         <v>217</v>
       </c>
-      <c r="J3" s="202" t="s">
+      <c r="L3" s="180" t="s">
         <v>218</v>
       </c>
-      <c r="K3" s="203" t="s">
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="181">
+        <v>1</v>
+      </c>
+      <c r="B4" s="182"/>
+      <c r="C4" s="183" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" s="183" t="s">
         <v>219</v>
       </c>
-      <c r="L3" s="204" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="205">
-        <v>1</v>
-      </c>
-      <c r="B4" s="206"/>
-      <c r="C4" s="207" t="s">
-        <v>31</v>
-      </c>
-      <c r="D4" s="207" t="s">
-        <v>221</v>
-      </c>
-      <c r="E4" s="208"/>
-      <c r="F4" s="209"/>
-      <c r="G4" s="209"/>
-      <c r="H4" s="210"/>
-      <c r="I4" s="208">
+      <c r="E4" s="184"/>
+      <c r="F4" s="185"/>
+      <c r="G4" s="185"/>
+      <c r="H4" s="186"/>
+      <c r="I4" s="184">
         <v>170</v>
       </c>
-      <c r="J4" s="211">
+      <c r="J4" s="187">
         <v>40</v>
       </c>
-      <c r="K4" s="212">
+      <c r="K4" s="188">
         <f>(I4+J4)*1.1*15%</f>
         <v>34.650000000000006</v>
       </c>
-      <c r="L4" s="209">
+      <c r="L4" s="185">
         <f>K4*5200</f>
         <v>180180.00000000003</v>
       </c>
     </row>
     <row r="5" spans="1:12">
-      <c r="A5" s="205">
+      <c r="A5" s="181">
         <v>2</v>
       </c>
-      <c r="B5" s="206"/>
-      <c r="C5" s="207" t="s">
-        <v>222</v>
-      </c>
-      <c r="D5" s="207" t="s">
+      <c r="B5" s="182"/>
+      <c r="C5" s="183" t="s">
+        <v>220</v>
+      </c>
+      <c r="D5" s="183" t="s">
         <v>62</v>
       </c>
-      <c r="E5" s="208"/>
-      <c r="F5" s="209"/>
-      <c r="G5" s="209"/>
-      <c r="H5" s="210"/>
-      <c r="I5" s="208"/>
-      <c r="J5" s="211"/>
-      <c r="K5" s="212">
+      <c r="E5" s="184"/>
+      <c r="F5" s="185"/>
+      <c r="G5" s="185"/>
+      <c r="H5" s="186"/>
+      <c r="I5" s="184"/>
+      <c r="J5" s="187"/>
+      <c r="K5" s="188">
         <f t="shared" ref="K5" si="0">(I5+J5)*1.1*15%</f>
         <v>0</v>
       </c>
-      <c r="L5" s="209">
+      <c r="L5" s="185">
         <f t="shared" ref="L5" si="1">K5*5200</f>
         <v>0</v>
       </c>
@@ -55516,58 +55545,58 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="213" t="s">
+      <c r="A1" s="189" t="s">
+        <v>221</v>
+      </c>
+      <c r="B1" s="190" t="s">
+        <v>201</v>
+      </c>
+      <c r="C1" s="190" t="s">
+        <v>202</v>
+      </c>
+      <c r="D1" s="190" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="191" t="s">
         <v>223</v>
       </c>
-      <c r="B1" s="214" t="s">
-        <v>201</v>
-      </c>
-      <c r="C1" s="214" t="s">
-        <v>202</v>
-      </c>
-      <c r="D1" s="214" t="s">
+      <c r="B2" s="191" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="215" t="s">
+      <c r="C2" s="192" t="s">
         <v>225</v>
       </c>
-      <c r="B2" s="215" t="s">
+      <c r="D2" s="193">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="194" t="s">
         <v>226</v>
       </c>
-      <c r="C2" s="216" t="s">
+      <c r="B3" s="194" t="s">
         <v>227</v>
       </c>
-      <c r="D2" s="217">
-        <v>25000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="218" t="s">
+      <c r="C3" s="195" t="s">
         <v>228</v>
       </c>
-      <c r="B3" s="218" t="s">
+      <c r="D3" s="196">
+        <v>165000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="191" t="s">
         <v>229</v>
       </c>
-      <c r="C3" s="219" t="s">
+      <c r="B4" s="191" t="s">
+        <v>227</v>
+      </c>
+      <c r="C4" s="192" t="s">
         <v>230</v>
       </c>
-      <c r="D3" s="220">
-        <v>165000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="215" t="s">
-        <v>231</v>
-      </c>
-      <c r="B4" s="215" t="s">
-        <v>229</v>
-      </c>
-      <c r="C4" s="216" t="s">
-        <v>232</v>
-      </c>
-      <c r="D4" s="217">
+      <c r="D4" s="193">
         <v>55000</v>
       </c>
     </row>
@@ -55594,30 +55623,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="225" t="s">
+      <c r="A1" s="201" t="s">
+        <v>231</v>
+      </c>
+      <c r="B1" s="201" t="s">
+        <v>232</v>
+      </c>
+      <c r="C1" s="202" t="s">
         <v>233</v>
       </c>
-      <c r="B1" s="225" t="s">
+      <c r="D1" s="202" t="s">
         <v>234</v>
       </c>
-      <c r="C1" s="226" t="s">
-        <v>235</v>
-      </c>
-      <c r="D1" s="226" t="s">
-        <v>236</v>
-      </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="215"/>
-      <c r="B2" s="227"/>
-      <c r="C2" s="228"/>
-      <c r="D2" s="228"/>
+      <c r="A2" s="191"/>
+      <c r="B2" s="203"/>
+      <c r="C2" s="204"/>
+      <c r="D2" s="204"/>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="221"/>
-      <c r="B3" s="222"/>
-      <c r="C3" s="223"/>
-      <c r="D3" s="224"/>
+      <c r="A3" s="197"/>
+      <c r="B3" s="198"/>
+      <c r="C3" s="199"/>
+      <c r="D3" s="200"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data-hotel.xlsx
+++ b/data-hotel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Donnée 2025\yeiayel consulting\Excel\LAHIMENA TOURS\Excel\Lahimena\ApiOK\Lahimena\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35FEF6F9-0691-4310-AFD3-53CFDF86C735}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99B929C2-3441-4E40-A07E-926648004C62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BDD_HOTEL" sheetId="1" r:id="rId1"/>
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="661" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="665" uniqueCount="244">
   <si>
     <t>Hotel</t>
   </si>
@@ -807,6 +807,15 @@
   </si>
   <si>
     <t>Guide full fort dauphin</t>
+  </si>
+  <si>
+    <t>fort Dauphin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antananarivo </t>
+  </si>
+  <si>
+    <t>Sambava</t>
   </si>
 </sst>
 </file>
@@ -2131,6 +2140,9 @@
     </xf>
     <xf numFmtId="168" fontId="10" fillId="20" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="10" fillId="20" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2189,9 +2201,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="13" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2504,24 +2513,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:49" ht="15" customHeight="1">
-      <c r="A1" s="211" t="s">
+      <c r="A1" s="212" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="212"/>
+      <c r="B1" s="213"/>
       <c r="C1" s="1"/>
-      <c r="D1" s="213"/>
-      <c r="E1" s="209"/>
+      <c r="D1" s="214"/>
+      <c r="E1" s="210"/>
       <c r="F1" s="2"/>
-      <c r="G1" s="214" t="s">
+      <c r="G1" s="215" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="206"/>
-      <c r="I1" s="206"/>
-      <c r="J1" s="206"/>
-      <c r="K1" s="206"/>
-      <c r="L1" s="206"/>
-      <c r="M1" s="206"/>
-      <c r="N1" s="206"/>
+      <c r="H1" s="207"/>
+      <c r="I1" s="207"/>
+      <c r="J1" s="207"/>
+      <c r="K1" s="207"/>
+      <c r="L1" s="207"/>
+      <c r="M1" s="207"/>
+      <c r="N1" s="207"/>
       <c r="O1" s="3"/>
       <c r="P1" s="3"/>
       <c r="Q1" s="3"/>
@@ -2531,43 +2540,43 @@
       <c r="S1" s="3"/>
       <c r="T1" s="3"/>
       <c r="U1" s="3"/>
-      <c r="V1" s="215" t="s">
+      <c r="V1" s="216" t="s">
         <v>3</v>
       </c>
-      <c r="W1" s="206"/>
-      <c r="X1" s="206"/>
-      <c r="Y1" s="206"/>
-      <c r="Z1" s="206"/>
-      <c r="AA1" s="209"/>
-      <c r="AB1" s="216" t="s">
+      <c r="W1" s="207"/>
+      <c r="X1" s="207"/>
+      <c r="Y1" s="207"/>
+      <c r="Z1" s="207"/>
+      <c r="AA1" s="210"/>
+      <c r="AB1" s="217" t="s">
         <v>4</v>
       </c>
-      <c r="AC1" s="206"/>
-      <c r="AD1" s="206"/>
-      <c r="AE1" s="206"/>
-      <c r="AF1" s="206"/>
-      <c r="AG1" s="206"/>
-      <c r="AH1" s="206"/>
-      <c r="AI1" s="209"/>
-      <c r="AJ1" s="205" t="s">
+      <c r="AC1" s="207"/>
+      <c r="AD1" s="207"/>
+      <c r="AE1" s="207"/>
+      <c r="AF1" s="207"/>
+      <c r="AG1" s="207"/>
+      <c r="AH1" s="207"/>
+      <c r="AI1" s="210"/>
+      <c r="AJ1" s="206" t="s">
         <v>5</v>
       </c>
-      <c r="AK1" s="206"/>
-      <c r="AL1" s="206"/>
-      <c r="AM1" s="206"/>
-      <c r="AN1" s="206"/>
-      <c r="AO1" s="206"/>
-      <c r="AP1" s="207"/>
+      <c r="AK1" s="207"/>
+      <c r="AL1" s="207"/>
+      <c r="AM1" s="207"/>
+      <c r="AN1" s="207"/>
+      <c r="AO1" s="207"/>
+      <c r="AP1" s="208"/>
       <c r="AQ1" s="5"/>
-      <c r="AR1" s="208" t="s">
+      <c r="AR1" s="209" t="s">
         <v>6</v>
       </c>
-      <c r="AS1" s="209"/>
-      <c r="AT1" s="210" t="s">
+      <c r="AS1" s="210"/>
+      <c r="AT1" s="211" t="s">
         <v>7</v>
       </c>
-      <c r="AU1" s="206"/>
-      <c r="AV1" s="209"/>
+      <c r="AU1" s="207"/>
+      <c r="AV1" s="210"/>
       <c r="AW1" s="6" t="s">
         <v>8</v>
       </c>
@@ -55323,7 +55332,7 @@
       <c r="D1" s="171" t="s">
         <v>203</v>
       </c>
-      <c r="E1" s="228" t="s">
+      <c r="E1" s="205" t="s">
         <v>165</v>
       </c>
     </row>
@@ -55389,38 +55398,38 @@
     <row r="1" spans="1:12">
       <c r="A1" s="172"/>
       <c r="B1" s="172"/>
-      <c r="C1" s="217" t="s">
+      <c r="C1" s="218" t="s">
         <v>204</v>
       </c>
-      <c r="D1" s="217"/>
-      <c r="E1" s="218" t="s">
+      <c r="D1" s="218"/>
+      <c r="E1" s="219" t="s">
         <v>205</v>
       </c>
-      <c r="F1" s="218"/>
-      <c r="G1" s="218"/>
-      <c r="H1" s="219"/>
-      <c r="I1" s="222" t="s">
+      <c r="F1" s="219"/>
+      <c r="G1" s="219"/>
+      <c r="H1" s="220"/>
+      <c r="I1" s="223" t="s">
         <v>206</v>
       </c>
-      <c r="J1" s="222"/>
-      <c r="K1" s="224" t="s">
+      <c r="J1" s="223"/>
+      <c r="K1" s="225" t="s">
         <v>207</v>
       </c>
-      <c r="L1" s="225"/>
+      <c r="L1" s="226"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="172"/>
       <c r="B2" s="172"/>
-      <c r="C2" s="217"/>
-      <c r="D2" s="217"/>
-      <c r="E2" s="220"/>
-      <c r="F2" s="220"/>
-      <c r="G2" s="220"/>
-      <c r="H2" s="221"/>
-      <c r="I2" s="223"/>
-      <c r="J2" s="223"/>
-      <c r="K2" s="226"/>
-      <c r="L2" s="227"/>
+      <c r="C2" s="218"/>
+      <c r="D2" s="218"/>
+      <c r="E2" s="221"/>
+      <c r="F2" s="221"/>
+      <c r="G2" s="221"/>
+      <c r="H2" s="222"/>
+      <c r="I2" s="224"/>
+      <c r="J2" s="224"/>
+      <c r="K2" s="227"/>
+      <c r="L2" s="228"/>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="173" t="s">
@@ -55637,16 +55646,32 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="191"/>
-      <c r="B2" s="203"/>
-      <c r="C2" s="204"/>
-      <c r="D2" s="204"/>
+      <c r="A2" s="191" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" s="203" t="s">
+        <v>241</v>
+      </c>
+      <c r="C2" s="204">
+        <v>500000</v>
+      </c>
+      <c r="D2" s="204">
+        <v>450000</v>
+      </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="197"/>
-      <c r="B3" s="198"/>
-      <c r="C3" s="199"/>
-      <c r="D3" s="200"/>
+      <c r="A3" s="197" t="s">
+        <v>242</v>
+      </c>
+      <c r="B3" s="198" t="s">
+        <v>243</v>
+      </c>
+      <c r="C3" s="199">
+        <v>1000000</v>
+      </c>
+      <c r="D3" s="200">
+        <v>950000</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data-hotel.xlsx
+++ b/data-hotel.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Donnée 2025\yeiayel consulting\Excel\LAHIMENA TOURS\Excel\Lahimena\ApiOK\Lahimena\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99B929C2-3441-4E40-A07E-926648004C62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57BE2785-FCE5-41AF-9244-52D44381D84B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BDD_HOTEL" sheetId="1" r:id="rId1"/>
     <sheet name="Circuits" sheetId="2" r:id="rId2"/>
     <sheet name="Frais collectifs" sheetId="3" r:id="rId3"/>
     <sheet name="Transport" sheetId="4" r:id="rId4"/>
-    <sheet name="Visite&amp;excursion" sheetId="5" r:id="rId5"/>
+    <sheet name="Visite_excursion" sheetId="5" r:id="rId5"/>
     <sheet name="Avion" sheetId="6" r:id="rId6"/>
   </sheets>
   <externalReferences>
